--- a/exports/trend_1d/CONCOR_full_report.xlsx
+++ b/exports/trend_1d/CONCOR_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>7.4</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42207</v>
+        <v>42208</v>
       </c>
       <c r="H2" t="n">
-        <v>446.4</v>
+        <v>423.6</v>
       </c>
       <c r="I2" t="n">
         <v>431.2951429857148</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K2" t="n">
-        <v>26.24</v>
+        <v>19.8</v>
       </c>
       <c r="L2" t="n">
         <v>4.43</v>
       </c>
       <c r="M2" t="n">
-        <v>2.73</v>
+        <v>3.83</v>
       </c>
       <c r="N2" t="n">
-        <v>4.56</v>
+        <v>5.11</v>
       </c>
       <c r="O2" t="n">
         <v>0.99</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14.22</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42258</v>
+        <v>42261</v>
       </c>
       <c r="H3" t="n">
-        <v>380.15</v>
+        <v>387.1</v>
       </c>
       <c r="I3" t="n">
         <v>383.086401408421</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K3" t="n">
-        <v>10.26</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L3" t="n">
         <v>3.34</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>15.68</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42298</v>
+        <v>42300</v>
       </c>
       <c r="H4" t="n">
-        <v>376.4</v>
+        <v>346.9</v>
       </c>
       <c r="I4" t="n">
         <v>348.5529388834645</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.76</v>
+        <v>-10.38</v>
       </c>
       <c r="L4" t="n">
         <v>13.3</v>
@@ -669,7 +716,7 @@
         <v>1.25</v>
       </c>
       <c r="N4" t="n">
-        <v>5.68</v>
+        <v>7.84</v>
       </c>
       <c r="O4" t="n">
         <v>1.83</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>18.22</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42432</v>
+        <v>42433</v>
       </c>
       <c r="H5" t="n">
-        <v>305.15</v>
+        <v>316.65</v>
       </c>
       <c r="I5" t="n">
         <v>312.6922276483332</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K5" t="n">
-        <v>12.04</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>9.58</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.13</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42593</v>
+        <v>42594</v>
       </c>
       <c r="H6" t="n">
-        <v>363.25</v>
+        <v>357.8</v>
       </c>
       <c r="I6" t="n">
         <v>358.2156232878261</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K6" t="n">
-        <v>14.72</v>
+        <v>13</v>
       </c>
       <c r="L6" t="n">
         <v>8.119999999999999</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.02</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42647</v>
+        <v>42648</v>
       </c>
       <c r="H7" t="n">
-        <v>353.75</v>
+        <v>359.45</v>
       </c>
       <c r="I7" t="n">
         <v>355.479840956622</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K7" t="n">
-        <v>1.13</v>
+        <v>-0.46</v>
       </c>
       <c r="L7" t="n">
         <v>2.81</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.75</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42689</v>
+        <v>42690</v>
       </c>
       <c r="H8" t="n">
-        <v>333.9</v>
+        <v>328.55</v>
       </c>
       <c r="I8" t="n">
         <v>333.4653691056636</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.11</v>
+        <v>-8.6</v>
       </c>
       <c r="L8" t="n">
         <v>10.1</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>12.62</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42737</v>
+        <v>42738</v>
       </c>
       <c r="H9" t="n">
-        <v>292.1</v>
+        <v>301.25</v>
       </c>
       <c r="I9" t="n">
         <v>300.3523288772124</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K9" t="n">
-        <v>11.09</v>
+        <v>8.31</v>
       </c>
       <c r="L9" t="n">
         <v>4.03</v>
       </c>
       <c r="M9" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="N9" t="n">
         <v>5.09</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42788</v>
+        <v>42789</v>
       </c>
       <c r="H10" t="n">
-        <v>311</v>
+        <v>303.75</v>
       </c>
       <c r="I10" t="n">
         <v>310.4959402780249</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K10" t="n">
-        <v>3.24</v>
+        <v>0.83</v>
       </c>
       <c r="L10" t="n">
         <v>3.47</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42830</v>
+        <v>42831</v>
       </c>
       <c r="H11" t="n">
-        <v>324.1</v>
+        <v>336.6</v>
       </c>
       <c r="I11" t="n">
         <v>332.9799036535229</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.7</v>
+        <v>-10.81</v>
       </c>
       <c r="L11" t="n">
-        <v>8.58</v>
+        <v>11.67</v>
       </c>
       <c r="M11" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.62</v>
+        <v>3.86</v>
       </c>
       <c r="O11" t="n">
         <v>-2.33</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H12" t="n">
-        <v>412.3</v>
+        <v>404.05</v>
       </c>
       <c r="I12" t="n">
         <v>407.7865069647276</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K12" t="n">
-        <v>22.49</v>
+        <v>20.04</v>
       </c>
       <c r="L12" t="n">
         <v>2.67</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>10.32</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43091</v>
+        <v>43095</v>
       </c>
       <c r="H13" t="n">
-        <v>436.15</v>
+        <v>446.15</v>
       </c>
       <c r="I13" t="n">
         <v>436.7664490033261</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.94</v>
+        <v>-10.42</v>
       </c>
       <c r="L13" t="n">
         <v>12.3</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>6.8</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H14" t="n">
-        <v>443.95</v>
+        <v>428.05</v>
       </c>
       <c r="I14" t="n">
         <v>437.9936908047695</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.49</v>
+        <v>-4.06</v>
       </c>
       <c r="L14" t="n">
-        <v>3.53</v>
+        <v>5.32</v>
       </c>
       <c r="M14" t="n">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="O14" t="n">
         <v>2.29</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.95</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43199</v>
+        <v>43200</v>
       </c>
       <c r="H15" t="n">
-        <v>403.8</v>
+        <v>408.55</v>
       </c>
       <c r="I15" t="n">
         <v>408.2050897327973</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K15" t="n">
-        <v>5.67</v>
+        <v>4.56</v>
       </c>
       <c r="L15" t="n">
         <v>2.86</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>7.57</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43265</v>
+        <v>43266</v>
       </c>
       <c r="H16" t="n">
-        <v>417.35</v>
+        <v>404.2</v>
       </c>
       <c r="I16" t="n">
         <v>410.4084180143223</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K16" t="n">
-        <v>2.15</v>
+        <v>-1.06</v>
       </c>
       <c r="L16" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="M16" t="n">
         <v>1.17</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>10.77</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43403</v>
+        <v>43404</v>
       </c>
       <c r="H17" t="n">
-        <v>398.95</v>
+        <v>405.6</v>
       </c>
       <c r="I17" t="n">
         <v>400.5489773118463</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3</v>
+        <v>-0.35</v>
       </c>
       <c r="L17" t="n">
         <v>8.76</v>
       </c>
       <c r="M17" t="n">
-        <v>1.52</v>
+        <v>2.34</v>
       </c>
       <c r="N17" t="n">
         <v>7.9</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>15.9</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H18" t="n">
-        <v>422.65</v>
+        <v>411.5</v>
       </c>
       <c r="I18" t="n">
         <v>413.0584317113996</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>1.45</v>
       </c>
       <c r="L18" t="n">
         <v>4.54</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43536</v>
+        <v>43537</v>
       </c>
       <c r="H19" t="n">
-        <v>402.45</v>
+        <v>418.05</v>
       </c>
       <c r="I19" t="n">
         <v>414.8386829026412</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2</v>
+        <v>-1.59</v>
       </c>
       <c r="L19" t="n">
         <v>7.41</v>
@@ -1524,7 +1751,7 @@
         <v>4.19</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>3.88</v>
       </c>
       <c r="O19" t="n">
         <v>-2.64</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>9.19</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43579</v>
+        <v>43580</v>
       </c>
       <c r="H20" t="n">
-        <v>402.85</v>
+        <v>393.75</v>
       </c>
       <c r="I20" t="n">
         <v>398.1428768898469</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.64</v>
+        <v>-5.81</v>
       </c>
       <c r="L20" t="n">
-        <v>4.82</v>
+        <v>6.52</v>
       </c>
       <c r="M20" t="n">
         <v>0.9</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>9.35</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43609</v>
+        <v>43612</v>
       </c>
       <c r="H21" t="n">
-        <v>404.45</v>
+        <v>418.7</v>
       </c>
       <c r="I21" t="n">
         <v>408.536847548405</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.72</v>
+        <v>-6.34</v>
       </c>
       <c r="L21" t="n">
-        <v>5.83</v>
+        <v>6.97</v>
       </c>
       <c r="M21" t="n">
         <v>5.36</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>11.61</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43663</v>
+        <v>43664</v>
       </c>
       <c r="H22" t="n">
-        <v>441.35</v>
+        <v>431.15</v>
       </c>
       <c r="I22" t="n">
         <v>432.8694662987905</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K22" t="n">
-        <v>5.41</v>
+        <v>2.97</v>
       </c>
       <c r="L22" t="n">
         <v>4.07</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>8.57</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43712</v>
+        <v>43713</v>
       </c>
       <c r="H23" t="n">
-        <v>402.3</v>
+        <v>412.1</v>
       </c>
       <c r="I23" t="n">
         <v>406.9087732224748</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K23" t="n">
-        <v>6.69</v>
+        <v>4.42</v>
       </c>
       <c r="L23" t="n">
         <v>2.6</v>
@@ -1752,7 +2027,7 @@
         <v>0.68</v>
       </c>
       <c r="N23" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="O23" t="n">
         <v>-2.31</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>10.97</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43861</v>
+        <v>43862</v>
       </c>
       <c r="H24" t="n">
-        <v>453.6</v>
+        <v>434.2</v>
       </c>
       <c r="I24" t="n">
         <v>439.3174165279626</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K24" t="n">
-        <v>10.07</v>
+        <v>5.36</v>
       </c>
       <c r="L24" t="n">
         <v>3.25</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>10.62</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43865</v>
+        <v>43866</v>
       </c>
       <c r="H25" t="n">
-        <v>453.1</v>
+        <v>475.6</v>
       </c>
       <c r="I25" t="n">
         <v>471.5753812520973</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.35</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>6.68</v>
+        <v>10.55</v>
       </c>
       <c r="M25" t="n">
         <v>0.62</v>
       </c>
       <c r="N25" t="n">
-        <v>3.9</v>
+        <v>4.97</v>
       </c>
       <c r="O25" t="n">
         <v>-4.28</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>12.42</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43878</v>
+        <v>43879</v>
       </c>
       <c r="H26" t="n">
-        <v>441.1</v>
+        <v>428.4</v>
       </c>
       <c r="I26" t="n">
         <v>429.1736720672211</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>-7.25</v>
+        <v>-9.92</v>
       </c>
       <c r="L26" t="n">
-        <v>7.67</v>
+        <v>10.57</v>
       </c>
       <c r="M26" t="n">
         <v>0.98</v>
       </c>
       <c r="N26" t="n">
-        <v>1.65</v>
+        <v>2.88</v>
       </c>
       <c r="O26" t="n">
         <v>4.97</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.75</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H27" t="n">
-        <v>300.9</v>
+        <v>315.5</v>
       </c>
       <c r="I27" t="n">
         <v>314.4968240779767</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K27" t="n">
-        <v>29.76</v>
+        <v>26.35</v>
       </c>
       <c r="L27" t="n">
         <v>5.31</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>16.29</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44050</v>
+        <v>44053</v>
       </c>
       <c r="H28" t="n">
-        <v>364.7</v>
+        <v>309.1</v>
       </c>
       <c r="I28" t="n">
         <v>333.3870729287938</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K28" t="n">
-        <v>15.59</v>
+        <v>-2.03</v>
       </c>
       <c r="L28" t="n">
         <v>7.42</v>
@@ -2037,7 +2372,7 @@
         <v>5.1</v>
       </c>
       <c r="N28" t="n">
-        <v>4.92</v>
+        <v>15.25</v>
       </c>
       <c r="O28" t="n">
         <v>4.85</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>21.17</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44125</v>
+        <v>44126</v>
       </c>
       <c r="H29" t="n">
-        <v>313.4</v>
+        <v>316.75</v>
       </c>
       <c r="I29" t="n">
         <v>313.9203246949959</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.39</v>
+        <v>-2.47</v>
       </c>
       <c r="L29" t="n">
         <v>13.59</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.09</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44403</v>
+        <v>44404</v>
       </c>
       <c r="H30" t="n">
-        <v>526.6</v>
+        <v>511.3</v>
       </c>
       <c r="I30" t="n">
         <v>516.9099865127997</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K30" t="n">
-        <v>66.25</v>
+        <v>61.42</v>
       </c>
       <c r="L30" t="n">
         <v>7.8</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>188</v>
+        <v>189</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>10</v>
+      </c>
+      <c r="U30" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44410</v>
+        <v>44411</v>
       </c>
       <c r="H31" t="n">
-        <v>553.05</v>
+        <v>559.55</v>
       </c>
       <c r="I31" t="n">
         <v>553.8471150255978</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K31" t="n">
-        <v>-8.17</v>
+        <v>-9.44</v>
       </c>
       <c r="L31" t="n">
-        <v>8.609999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="M31" t="n">
         <v>4.55</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.77</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44487</v>
+        <v>44488</v>
       </c>
       <c r="H32" t="n">
-        <v>547.7</v>
+        <v>533.9</v>
       </c>
       <c r="I32" t="n">
         <v>539.9125890731227</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.12</v>
+        <v>-4.58</v>
       </c>
       <c r="L32" t="n">
         <v>8.779999999999999</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.21</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44572</v>
+        <v>44573</v>
       </c>
       <c r="H33" t="n">
-        <v>517.4</v>
+        <v>525.3</v>
       </c>
       <c r="I33" t="n">
         <v>524.0448551760529</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K33" t="n">
-        <v>3.09</v>
+        <v>1.61</v>
       </c>
       <c r="L33" t="n">
         <v>6.51</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>7.36</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44581</v>
+        <v>44582</v>
       </c>
       <c r="H34" t="n">
-        <v>528.35</v>
+        <v>498.9</v>
       </c>
       <c r="I34" t="n">
         <v>513.6213747274595</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K34" t="n">
-        <v>0.58</v>
+        <v>-5.03</v>
       </c>
       <c r="L34" t="n">
-        <v>1.71</v>
+        <v>5.73</v>
       </c>
       <c r="M34" t="n">
         <v>0.7</v>
       </c>
       <c r="N34" t="n">
-        <v>1.6</v>
+        <v>5.57</v>
       </c>
       <c r="O34" t="n">
         <v>1.53</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>12.56</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44644</v>
+        <v>44645</v>
       </c>
       <c r="H35" t="n">
-        <v>497.2</v>
+        <v>551.85</v>
       </c>
       <c r="I35" t="n">
         <v>499.2373496763215</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K35" t="n">
-        <v>0.34</v>
+        <v>-10.61</v>
       </c>
       <c r="L35" t="n">
-        <v>6.79</v>
+        <v>13.05</v>
       </c>
       <c r="M35" t="n">
         <v>2.08</v>
       </c>
       <c r="N35" t="n">
-        <v>4.43</v>
+        <v>10.99</v>
       </c>
       <c r="O35" t="n">
         <v>-5.57</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>14.59</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44690</v>
+        <v>44691</v>
       </c>
       <c r="H36" t="n">
-        <v>499.7</v>
+        <v>489.35</v>
       </c>
       <c r="I36" t="n">
         <v>499.6304099969425</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K36" t="n">
-        <v>-9.449999999999999</v>
+        <v>-11.33</v>
       </c>
       <c r="L36" t="n">
-        <v>10.1</v>
+        <v>11.74</v>
       </c>
       <c r="M36" t="n">
         <v>2</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>13.82</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44749</v>
+        <v>44750</v>
       </c>
       <c r="H37" t="n">
-        <v>522.45</v>
+        <v>525.3</v>
       </c>
       <c r="I37" t="n">
         <v>523.8170927305893</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.76</v>
+        <v>-7.35</v>
       </c>
       <c r="L37" t="n">
         <v>10.79</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.84</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44830</v>
+        <v>44831</v>
       </c>
       <c r="H38" t="n">
-        <v>558.7</v>
+        <v>548.5</v>
       </c>
       <c r="I38" t="n">
         <v>552.4846232617166</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K38" t="n">
-        <v>6.36</v>
+        <v>4.42</v>
       </c>
       <c r="L38" t="n">
         <v>0.82</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>12.29</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44852</v>
+        <v>44853</v>
       </c>
       <c r="H39" t="n">
-        <v>577.1</v>
+        <v>617</v>
       </c>
       <c r="I39" t="n">
         <v>603.4793136293439</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.21</v>
+        <v>-12.49</v>
       </c>
       <c r="L39" t="n">
-        <v>6.24</v>
+        <v>13.47</v>
       </c>
       <c r="M39" t="n">
         <v>2.81</v>
       </c>
       <c r="N39" t="n">
-        <v>2.46</v>
+        <v>6.91</v>
       </c>
       <c r="O39" t="n">
         <v>-1.83</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>13</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44883</v>
+        <v>44886</v>
       </c>
       <c r="H40" t="n">
-        <v>591.3</v>
+        <v>586.65</v>
       </c>
       <c r="I40" t="n">
         <v>588.3894285061782</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.17</v>
+        <v>-4.92</v>
       </c>
       <c r="L40" t="n">
         <v>6.47</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>9.73</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45028</v>
+        <v>45029</v>
       </c>
       <c r="H41" t="n">
-        <v>480.75</v>
+        <v>483.7</v>
       </c>
       <c r="I41" t="n">
         <v>482.8014050128973</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K41" t="n">
-        <v>18.05</v>
+        <v>17.55</v>
       </c>
       <c r="L41" t="n">
         <v>7.99</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>6</v>
+      </c>
+      <c r="U41" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.15</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45096</v>
+        <v>45097</v>
       </c>
       <c r="H42" t="n">
-        <v>528.75</v>
+        <v>509.1</v>
       </c>
       <c r="I42" t="n">
         <v>511.0330503106749</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K42" t="n">
-        <v>9.31</v>
+        <v>5.25</v>
       </c>
       <c r="L42" t="n">
         <v>1.74</v>
       </c>
       <c r="M42" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="N42" t="n">
-        <v>1.86</v>
+        <v>3.72</v>
       </c>
       <c r="O42" t="n">
         <v>0.61</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45112</v>
+        <v>45113</v>
       </c>
       <c r="H43" t="n">
-        <v>538.45</v>
+        <v>552</v>
       </c>
       <c r="I43" t="n">
         <v>551.9838366833286</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K43" t="n">
-        <v>-5.77</v>
+        <v>-8.43</v>
       </c>
       <c r="L43" t="n">
-        <v>6.44</v>
+        <v>8.67</v>
       </c>
       <c r="M43" t="n">
         <v>1.36</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45155</v>
+        <v>45156</v>
       </c>
       <c r="H44" t="n">
-        <v>528.85</v>
+        <v>523.8</v>
       </c>
       <c r="I44" t="n">
         <v>525.9936028147924</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.19</v>
+        <v>-5.11</v>
       </c>
       <c r="L44" t="n">
         <v>6.39</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45176</v>
+        <v>45177</v>
       </c>
       <c r="H45" t="n">
-        <v>552.75</v>
+        <v>567.1</v>
       </c>
       <c r="I45" t="n">
         <v>561.9409762934191</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.53</v>
+        <v>-8.27</v>
       </c>
       <c r="L45" t="n">
-        <v>7.67</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="M45" t="n">
         <v>0.98</v>
       </c>
       <c r="N45" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="O45" t="n">
         <v>-0.95</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>8.15</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45230</v>
+        <v>45231</v>
       </c>
       <c r="H46" t="n">
-        <v>550.55</v>
+        <v>540.4</v>
       </c>
       <c r="I46" t="n">
         <v>541.1947810462502</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.92</v>
+        <v>-4.71</v>
       </c>
       <c r="L46" t="n">
-        <v>4.78</v>
+        <v>5.18</v>
       </c>
       <c r="M46" t="n">
         <v>1.54</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>7.93</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45233</v>
+        <v>45236</v>
       </c>
       <c r="H47" t="n">
-        <v>571</v>
+        <v>587.8</v>
       </c>
       <c r="I47" t="n">
         <v>582.9425649842082</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.66</v>
+        <v>-8.77</v>
       </c>
       <c r="L47" t="n">
-        <v>6.56</v>
+        <v>9.84</v>
       </c>
       <c r="M47" t="n">
         <v>2.84</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H48" t="n">
-        <v>698.7</v>
+        <v>660.25</v>
       </c>
       <c r="I48" t="n">
         <v>664.3001651689013</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K48" t="n">
-        <v>18.87</v>
+        <v>12.33</v>
       </c>
       <c r="L48" t="n">
         <v>2.28</v>
@@ -3177,7 +3752,7 @@
         <v>0.99</v>
       </c>
       <c r="N48" t="n">
-        <v>3.69</v>
+        <v>5.5</v>
       </c>
       <c r="O48" t="n">
         <v>2.94</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>15.2</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45324</v>
+        <v>45327</v>
       </c>
       <c r="H49" t="n">
-        <v>736.05</v>
+        <v>744.3</v>
       </c>
       <c r="I49" t="n">
         <v>742.6618907504571</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K49" t="n">
-        <v>-11.48</v>
+        <v>-12.73</v>
       </c>
       <c r="L49" t="n">
-        <v>13.64</v>
+        <v>15.34</v>
       </c>
       <c r="M49" t="n">
         <v>1.72</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>11.05</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H50" t="n">
-        <v>740</v>
+        <v>689.95</v>
       </c>
       <c r="I50" t="n">
         <v>725.4576981979307</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.58</v>
+        <v>-7.3</v>
       </c>
       <c r="L50" t="n">
-        <v>3.91</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M50" t="n">
         <v>0.87</v>
       </c>
       <c r="N50" t="n">
-        <v>3.22</v>
+        <v>6.76</v>
       </c>
       <c r="O50" t="n">
         <v>1.12</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>14.76</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="H51" t="n">
-        <v>730.9</v>
+        <v>746.8</v>
       </c>
       <c r="I51" t="n">
         <v>745.070007709297</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.94</v>
+        <v>-8.24</v>
       </c>
       <c r="L51" t="n">
-        <v>7.68</v>
+        <v>9.25</v>
       </c>
       <c r="M51" t="n">
         <v>1.35</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H52" t="n">
-        <v>939.4</v>
+        <v>759</v>
       </c>
       <c r="I52" t="n">
         <v>815.0490397164788</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K52" t="n">
-        <v>25.79</v>
+        <v>1.63</v>
       </c>
       <c r="L52" t="n">
-        <v>4.45</v>
+        <v>5.66</v>
       </c>
       <c r="M52" t="n">
         <v>1.34</v>
       </c>
       <c r="N52" t="n">
-        <v>2.91</v>
+        <v>19.2</v>
       </c>
       <c r="O52" t="n">
         <v>2.18</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>29.8</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="H53" t="n">
-        <v>671.9</v>
+        <v>675.4</v>
       </c>
       <c r="I53" t="n">
         <v>675.1085375444925</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K53" t="n">
-        <v>11.48</v>
+        <v>11.01</v>
       </c>
       <c r="L53" t="n">
         <v>24.37</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>7</v>
+      </c>
+      <c r="U53" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>6.83</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45643</v>
+        <v>45644</v>
       </c>
       <c r="H54" t="n">
-        <v>645</v>
+        <v>638.9</v>
       </c>
       <c r="I54" t="n">
         <v>643.2459751025298</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.5</v>
+        <v>-5.4</v>
       </c>
       <c r="L54" t="n">
-        <v>4.65</v>
+        <v>5.89</v>
       </c>
       <c r="M54" t="n">
         <v>1.45</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>7.3</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H55" t="n">
-        <v>551.7</v>
+        <v>572.75</v>
       </c>
       <c r="I55" t="n">
         <v>555.4953489365529</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K55" t="n">
-        <v>13.65</v>
+        <v>10.35</v>
       </c>
       <c r="L55" t="n">
         <v>1.47</v>
       </c>
       <c r="M55" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="N55" t="n">
         <v>5.47</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>10.84</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H56" t="n">
-        <v>550</v>
+        <v>519.4</v>
       </c>
       <c r="I56" t="n">
         <v>520.7039381997107</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.97</v>
+        <v>-9.31</v>
       </c>
       <c r="L56" t="n">
-        <v>4.65</v>
+        <v>10.45</v>
       </c>
       <c r="M56" t="n">
-        <v>1.87</v>
+        <v>6.62</v>
       </c>
       <c r="N56" t="n">
-        <v>3.78</v>
+        <v>5.56</v>
       </c>
       <c r="O56" t="n">
         <v>3.82</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>12.71</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45792</v>
+        <v>45793</v>
       </c>
       <c r="H57" t="n">
-        <v>552.2</v>
+        <v>584.4</v>
       </c>
       <c r="I57" t="n">
         <v>569.4240864118904</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K57" t="n">
-        <v>-6.31</v>
+        <v>-12.51</v>
       </c>
       <c r="L57" t="n">
-        <v>10.41</v>
+        <v>13.05</v>
       </c>
       <c r="M57" t="n">
         <v>3.31</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>11.75</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45825</v>
+        <v>45826</v>
       </c>
       <c r="H58" t="n">
-        <v>600.6</v>
+        <v>596.6</v>
       </c>
       <c r="I58" t="n">
         <v>596.8401524111067</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K58" t="n">
-        <v>2.77</v>
+        <v>2.09</v>
       </c>
       <c r="L58" t="n">
         <v>5.6</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>8.32</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="H59" t="n">
-        <v>556</v>
+        <v>564.15</v>
       </c>
       <c r="I59" t="n">
         <v>561.935092088122</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K59" t="n">
-        <v>6.81</v>
+        <v>5.44</v>
       </c>
       <c r="L59" t="n">
         <v>5.46</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>5.95</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="H60" t="n">
-        <v>543.75</v>
+        <v>530.8</v>
       </c>
       <c r="I60" t="n">
         <v>531.4869114588478</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.62</v>
+        <v>-5.91</v>
       </c>
       <c r="L60" t="n">
-        <v>3.84</v>
+        <v>6.2</v>
       </c>
       <c r="M60" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="N60" t="n">
-        <v>1.31</v>
+        <v>2.38</v>
       </c>
       <c r="O60" t="n">
         <v>1.47</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.52</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="H61" t="n">
-        <v>519</v>
+        <v>524.95</v>
       </c>
       <c r="I61" t="n">
         <v>520.9644331188194</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K61" t="n">
-        <v>2.22</v>
+        <v>1.1</v>
       </c>
       <c r="L61" t="n">
         <v>4.94</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>5</v>
+      </c>
+      <c r="U61" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>5.81</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H62" t="n">
-        <v>514.9</v>
+        <v>497.85</v>
       </c>
       <c r="I62" t="n">
         <v>504.6827338948705</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.91</v>
+        <v>-5.16</v>
       </c>
       <c r="L62" t="n">
-        <v>3.91</v>
+        <v>5.7</v>
       </c>
       <c r="M62" t="n">
         <v>0.59</v>
       </c>
       <c r="N62" t="n">
-        <v>2.68</v>
+        <v>3.31</v>
       </c>
       <c r="O62" t="n">
         <v>1.15</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>7.75</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H63" t="n">
-        <v>507.85</v>
+        <v>527.9</v>
       </c>
       <c r="I63" t="n">
         <v>517.1606818494018</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.01</v>
+        <v>-6.04</v>
       </c>
       <c r="L63" t="n">
-        <v>5.37</v>
+        <v>8.26</v>
       </c>
       <c r="M63" t="n">
-        <v>0.63</v>
+        <v>4.36</v>
       </c>
       <c r="N63" t="n">
-        <v>2.27</v>
+        <v>3.95</v>
       </c>
       <c r="O63" t="n">
         <v>-3.31</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>9.59</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H64" t="n">
-        <v>479</v>
+        <v>462.2</v>
       </c>
       <c r="I64" t="n">
         <v>477.265931677272</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K64" t="n">
-        <v>-9.26</v>
+        <v>-12.45</v>
       </c>
       <c r="L64" t="n">
-        <v>10.07</v>
+        <v>12.78</v>
       </c>
       <c r="M64" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="N64" t="n">
-        <v>3.36</v>
+        <v>3.51</v>
       </c>
       <c r="O64" t="n">
         <v>3.95</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>8.85</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H65" t="n">
-        <v>453.6</v>
+        <v>473.7</v>
       </c>
       <c r="I65" t="n">
         <v>473.4623732804297</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K65" t="n">
-        <v>1.86</v>
+        <v>-2.49</v>
       </c>
       <c r="L65" t="n">
         <v>5.8</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>11.15</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="H66" t="n">
-        <v>512.05</v>
+        <v>475.9</v>
       </c>
       <c r="I66" t="n">
         <v>497.9552267565231</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K66" t="n">
-        <v>8.1</v>
+        <v>0.46</v>
       </c>
       <c r="L66" t="n">
         <v>2.08</v>
       </c>
       <c r="M66" t="n">
-        <v>1.57</v>
+        <v>4.15</v>
       </c>
       <c r="N66" t="n">
-        <v>3.25</v>
+        <v>7.06</v>
       </c>
       <c r="O66" t="n">
         <v>4.43</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>10.66</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="H67" t="n">
-        <v>473.65</v>
+        <v>479.25</v>
       </c>
       <c r="I67" t="n">
         <v>475.8540410294361</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K67" t="n">
-        <v>0.47</v>
+        <v>-0.7</v>
       </c>
       <c r="L67" t="n">
         <v>3.99</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>6.71</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="H68" t="n">
-        <v>472.75</v>
+        <v>451.4</v>
       </c>
       <c r="I68" t="n">
         <v>453.5115930464634</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.36</v>
+        <v>-5.81</v>
       </c>
       <c r="L68" t="n">
-        <v>2.88</v>
+        <v>6.43</v>
       </c>
       <c r="M68" t="n">
-        <v>0.47</v>
+        <v>0.79</v>
       </c>
       <c r="N68" t="n">
-        <v>1.78</v>
+        <v>4.52</v>
       </c>
       <c r="O68" t="n">
         <v>1.18</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>9.85</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="H69" t="n">
-        <v>463.95</v>
+        <v>493.15</v>
       </c>
       <c r="I69" t="n">
         <v>491.7498736691282</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.78</v>
+        <v>-9.25</v>
       </c>
       <c r="L69" t="n">
-        <v>4.24</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M69" t="n">
         <v>1.07</v>
       </c>
       <c r="N69" t="n">
-        <v>1.45</v>
+        <v>6.29</v>
       </c>
       <c r="O69" t="n">
         <v>-4.52</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>10.91</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="H70" t="n">
-        <v>517</v>
+        <v>493.05</v>
       </c>
       <c r="I70" t="n">
         <v>493.8330586636397</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K70" t="n">
-        <v>4.84</v>
+        <v>-0.02</v>
       </c>
       <c r="L70" t="n">
         <v>5.08</v>
@@ -4431,7 +5270,7 @@
         <v>1.58</v>
       </c>
       <c r="N70" t="n">
-        <v>2.08</v>
+        <v>4.63</v>
       </c>
       <c r="O70" t="n">
         <v>6.29</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>42</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9449,7 +10308,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.1</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="6">
@@ -9459,7 +10318,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -9469,7 +10328,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8">
@@ -9479,7 +10338,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -9489,7 +10348,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -9499,7 +10358,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -9509,7 +10368,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -9519,7 +10378,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -9529,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.4</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="14">
@@ -9539,7 +10398,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.29</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="15">
@@ -9549,7 +10408,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.08</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="16">
@@ -9559,7 +10418,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.45</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="17">
@@ -9569,7 +10428,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>66.25</v>
+        <v>61.42</v>
       </c>
     </row>
     <row r="18">
@@ -9579,7 +10438,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.2</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="19">
@@ -9589,7 +10448,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.22</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="20">
@@ -9599,7 +10458,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.46</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="21">
@@ -9619,7 +10478,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -9629,7 +10488,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -9639,7 +10498,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="25">
@@ -9649,7 +10508,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.44</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="26">
@@ -9659,7 +10518,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.95</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="27">
@@ -9669,7 +10528,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.09</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="28">
@@ -9679,7 +10538,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
